--- a/data/processed_data/Video_466_EXP5_FAPS4_40V/contracciones.xlsx
+++ b/data/processed_data/Video_466_EXP5_FAPS4_40V/contracciones.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="estab_Video_466_EXP5_FAPS4" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="resumen_Video_466_EXP5_FAP" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ritmo_Video_466_EXP5_FAPS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="grilla_Video_466_EXP5_FAP" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="eventos_Video_466_EXP5_FAP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="estab_Video_466_EXP5_FAPS4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumen_Video_466_EXP5_FAP" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ritmo_Video_466_EXP5_FAPS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="grilla_Video_466_EXP5_FAP" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eventos_Video_466_EXP5_FAP" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,16 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,22 +421,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -459,13 +447,13 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6343</v>
+        <v>0.6349</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +461,13 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8457</v>
+        <v>0.8466</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -487,13 +475,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>1.2685</v>
+        <v>1.2698</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -501,7 +489,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>1.6914</v>
+        <v>1.6931</v>
       </c>
       <c r="C5" t="n">
         <v>5</v>
@@ -515,7 +503,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>2.1142</v>
+        <v>2.1164</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
@@ -529,7 +517,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>2.537</v>
+        <v>2.5397</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
@@ -543,7 +531,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>3.1713</v>
+        <v>3.1746</v>
       </c>
       <c r="C8" t="n">
         <v>5</v>
@@ -557,10 +545,10 @@
         <v>20</v>
       </c>
       <c r="B9" t="n">
-        <v>4.2284</v>
+        <v>4.2328</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -577,118 +565,138 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>k_usado</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>k_automatico</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>hay_meseta</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>meseta_motivo</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>meseta_k_rango</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>conteo_reportable</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>picos_con_sep_menor</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>amplitud_traslacion_px</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>ritmo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>fps_medido</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>adelgazamiento_px</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>adelgazamiento_sigma</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>blur_px</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>blur_sigma</t>
         </is>
       </c>
     </row>
@@ -699,80 +707,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.96609460025324</v>
+        <v>30.00000000000171</v>
       </c>
       <c r="C2" t="n">
         <v>2076</v>
       </c>
       <c r="D2" t="n">
-        <v>71.63547687861272</v>
+        <v>71.65333333333334</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2114187599999813</v>
+        <v>0.2116411499999676</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3324791540268542</v>
+        <v>0.3649915845233185</v>
       </c>
       <c r="H2" t="n">
         <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J2" t="n">
-        <v>9.804566473988444</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.763899999999978</v>
+        <v>4</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>{'n_eventos': 5, 'hay_estimulacion': True, 'estimulados': array([0, 1, 3, 4]), 'espontaneos': array([], dtype=int64), 'z': 10.887, 'p_valor': nan, 'periodo_grilla_s': 9.823, 'periodo_s': 9.85635, 'periodo_err_s': 0.01444, 'frecuencia_Hz': 0.10146, 'frecuencia_err_Hz': 0.000149, 'jitter_s': 0.02559, 'tolerancia_s': 0.1036, 'n_estimulados': 4, 'n_ranuras': 5, 'tasa_captura_pct': 80.0, 'tren_inicio_s': 14.534, 'tren_fin_s': 53.925, 'estimulados_dudosos': array([2]), 'n_estimulados_dudosos': 1, 'dudosos':    indice_evento  tiempo_s  ranura  desvio_s
-0              2     34.42       3    0.2071, 'resumen_grupos':                  grupo  n  ...  amplitud_mediana_px  amplitud_IQR_px
-0          estimulados  4  ...               3.6767           0.3389
-1  estimulados_dudosos  1  ...               3.7639           0.0000
-[2 rows x 10 columns], 'espontaneas_instantanea': Empty DataFrame
+          <t>meseta de 5 eventos en k=4..15 (6 puntos) con 0 falsos de control</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>4-15</t>
+        </is>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>7</v>
+      </c>
+      <c r="P2" t="n">
+        <v>9.987500000000004</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.293600000000026</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>{'n_eventos': 5, 'hay_estimulacion': True, 'estimulados': array([0, 1, 2, 3, 4]), 'espontaneos': array([], dtype=int64), 'z': 13.577, 'p_valor': nan, 'periodo_grilla_s': 10.0287, 'periodo_s': 9.99433, 'periodo_err_s': 0.01197, 'frecuencia_Hz': 0.10006, 'frecuencia_err_Hz': 0.00012, 'jitter_s': 0.03509, 'tolerancia_s': 0.1071, 'n_estimulados': 5, 'n_ranuras': 5, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 14.312, 'tren_fin_s': 54.322, 'estimulados_dudosos': array([], dtype=int64), 'resumen_grupos':          grupo  n  ...  amplitud_mediana_px  amplitud_IQR_px
+0  estimulados  5  ...               4.2936           0.4583
+[1 rows x 10 columns], 'espontaneas_instantanea': Empty DataFrame
 Columns: [tiempo_s, intervalo_s, frecuencia_Hz]
 Index: [], 'grilla':    ranura  t_esperado_s  t_medido_s  error_s  capturada
-0       1       14.4997     14.5342  0.03452       True
-1       2       24.3561     24.3043 -0.05178       True
-2       3       34.2124         NaN      NaN      False
-3       4       44.0688     44.0860  0.01726       True
-4       5       53.9251     53.9251 -0.00000       True}</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>28.96609460025324</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.4446047228517784</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.990161552605889</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-0.5868930635837728</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>12.1276560771781</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-0.4062667402324507</v>
+0       1       14.3060     14.3117  0.00567       True
+1       2       24.3003     24.3200  0.01967       True
+2       3       34.2947     34.2767 -0.01800       True
+3       4       44.2890     44.2433 -0.04567       True
+4       5       54.2833     54.3217  0.03833       True}</t>
+        </is>
       </c>
       <c r="S2" t="n">
-        <v>4.732520219632081</v>
+        <v>30.00000000000171</v>
       </c>
       <c r="T2" t="n">
-        <v>11.08189600311105</v>
+        <v>0.7528916758085472</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4772939200725205</v>
+        <v>4.612481597350608</v>
       </c>
       <c r="V2" t="n">
-        <v>3.210010725795172</v>
+        <v>-0.5999999999999659</v>
+      </c>
+      <c r="W2" t="n">
+        <v>17.9196777280517</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.2633470245440738</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.794416867623182</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>6.26795854184891</v>
       </c>
     </row>
   </sheetData>
@@ -786,56 +808,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_inicio_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_fin_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>intervalo_IQR_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_mediana_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>CV_intervalo_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>amplitud_mediana_px</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>amplitud_IQR_px</t>
         </is>
@@ -848,57 +870,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>14.53</v>
+        <v>14.31</v>
       </c>
       <c r="D2" t="n">
-        <v>53.93</v>
+        <v>54.32</v>
       </c>
       <c r="E2" t="n">
-        <v>9.8391</v>
+        <v>9.987500000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>5.0059</v>
+        <v>0.0617</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1016</v>
+        <v>0.1001</v>
       </c>
       <c r="H2" t="n">
-        <v>35.8</v>
+        <v>0.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6767</v>
+        <v>4.2936</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3389</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>estimulados_dudosos</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>34.42</v>
-      </c>
-      <c r="D3" t="n">
-        <v>34.42</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="n">
-        <v>3.7639</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
+        <v>0.4583</v>
       </c>
     </row>
   </sheetData>
@@ -916,27 +912,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ranura</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>t_esperado_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_medido_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>error_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>capturada</t>
         </is>
@@ -947,13 +943,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>14.4997</v>
+        <v>14.306</v>
       </c>
       <c r="C2" t="n">
-        <v>14.5342</v>
+        <v>14.3117</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03452</v>
+        <v>0.00567</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -964,13 +960,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>24.3561</v>
+        <v>24.3003</v>
       </c>
       <c r="C3" t="n">
-        <v>24.3043</v>
+        <v>24.32</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.05178</v>
+        <v>0.01967</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -981,12 +977,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>34.2124</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+        <v>34.2947</v>
+      </c>
+      <c r="C4" t="n">
+        <v>34.2767</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.018</v>
+      </c>
       <c r="E4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -994,13 +994,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>44.0688</v>
+        <v>44.289</v>
       </c>
       <c r="C5" t="n">
-        <v>44.086</v>
+        <v>44.2433</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01726</v>
+        <v>-0.04567</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -1011,13 +1011,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>53.9251</v>
+        <v>54.2833</v>
       </c>
       <c r="C6" t="n">
-        <v>53.9251</v>
+        <v>54.3217</v>
       </c>
       <c r="D6" t="n">
-        <v>-0</v>
+        <v>0.03833</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -1038,17 +1038,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
@@ -1059,10 +1059,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>14.53423410404624</v>
+        <v>14.31166666666667</v>
       </c>
       <c r="C2" t="n">
-        <v>3.254799999999989</v>
+        <v>3.863699999999994</v>
       </c>
     </row>
     <row r="3">
@@ -1070,10 +1070,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>24.3042774566474</v>
+        <v>24.32</v>
       </c>
       <c r="C3" t="n">
-        <v>3.785399999999981</v>
+        <v>3.965399999999988</v>
       </c>
     </row>
     <row r="4">
@@ -1081,10 +1081,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>34.41955202312139</v>
+        <v>34.27666666666667</v>
       </c>
       <c r="C4" t="n">
-        <v>3.763899999999978</v>
+        <v>4.293600000000026</v>
       </c>
     </row>
     <row r="5">
@@ -1092,10 +1092,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>44.0860260115607</v>
+        <v>44.24333333333335</v>
       </c>
       <c r="C5" t="n">
-        <v>3.567999999999984</v>
+        <v>4.461000000000013</v>
       </c>
     </row>
     <row r="6">
@@ -1103,10 +1103,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>53.92511560693642</v>
+        <v>54.32166666666667</v>
       </c>
       <c r="C6" t="n">
-        <v>3.958100000000002</v>
+        <v>4.423699999999997</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed_data/Video_466_EXP5_FAPS4_40V/contracciones.xlsx
+++ b/data/processed_data/Video_466_EXP5_FAPS4_40V/contracciones.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ritmo_Video_466_EXP5_FAPS" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="grilla_Video_466_EXP5_FAP" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eventos_Video_466_EXP5_FAP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cinetica_Video_466_EXP5_FAP" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -565,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:AR2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,6 +698,96 @@
       <c r="Z1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>cinetica_min_frames</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_iqr_pct</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>ttp_n_eventos</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>ttp_frames_mediana</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>ttp_reportable</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>ttp_iqr_s</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>ttp_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>ttp_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>rt50_n_eventos</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>rt50_frames_mediana</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>rt50_reportable</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>rt50_iqr_s</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>rt50_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>rt50_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>cinetica_motivo</t>
         </is>
       </c>
     </row>
@@ -795,6 +886,68 @@
       </c>
       <c r="Z2" t="n">
         <v>6.26795854184891</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.134093296607975</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1.97-2.195</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.2842709976597053</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.2563-0.2903</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1366666666666596</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.3649999999999984</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.1600804817649646</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.1445-0.1607</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.07000000000000028</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.2600000000000016</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>TTP y RT50 medibles</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1112,4 +1265,480 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>evento</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>grupo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>frame_pico</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tiempo_s</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>grosor_reposo_px</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>meseta_pico_frames</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>onset_s</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ttp_frames</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ttp_min_s</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ttp_max_s</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ttp_medible</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>rt50_frames</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>rt50_min_s</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>rt50_max_s</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>rt50_medible</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>offset_s</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>duracion_frames</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>duracion_s</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>422</v>
+      </c>
+      <c r="D2" t="n">
+        <v>14.31166666666667</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.863699999999994</v>
+      </c>
+      <c r="F2" t="n">
+        <v>201.1121664868647</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.921166713826011</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>14.02739566900696</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.2842709976597053</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.1366666666666596</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.3766666666666705</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1249238736546019</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.02500000000000036</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.2700000000000014</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>14.64498546625815</v>
+      </c>
+      <c r="U2" t="n">
+        <v>20</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.6175897972511848</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>706</v>
+      </c>
+      <c r="D3" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.965399999999988</v>
+      </c>
+      <c r="F3" t="n">
+        <v>201.2503244797527</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.970381916278072</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>24.02968855374078</v>
+      </c>
+      <c r="J3" t="n">
+        <v>9</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.2903114462592171</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1733333333333285</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.3649999999999984</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.1444839255499204</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.07000000000000028</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.2600000000000016</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>24.60785822401614</v>
+      </c>
+      <c r="U3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.5781696702753614</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>34.27666666666667</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.293600000000026</v>
+      </c>
+      <c r="F4" t="n">
+        <v>201.1908292305903</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.134093296607975</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>34.02041304655842</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2562536201082466</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.2050000000000054</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.36666666666666</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1607267264372325</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.03333333333333854</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.2066666666666706</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>34.59467108043386</v>
+      </c>
+      <c r="U4" t="n">
+        <v>18</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.5742580338754379</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1275</v>
+      </c>
+      <c r="D5" t="n">
+        <v>44.24333333333335</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.461000000000013</v>
+      </c>
+      <c r="F5" t="n">
+        <v>201.4650776355367</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.214279542814983</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>44.06655207232594</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.176781261007406</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.1033333333333317</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2433333333333323</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1913054372893299</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.123333333333342</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.259999999999998</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>44.6152236135957</v>
+      </c>
+      <c r="U5" t="n">
+        <v>18</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.548671541269762</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1562</v>
+      </c>
+      <c r="D6" t="n">
+        <v>54.32166666666667</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.423699999999997</v>
+      </c>
+      <c r="F6" t="n">
+        <v>201.5348332891158</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.195005165014769</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>54.02018076923077</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.3014858974359029</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.3616666666666717</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>6</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1600804817649646</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.09999999999999432</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.3783333333333303</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>54.69892963533642</v>
+      </c>
+      <c r="U6" t="n">
+        <v>21</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.67874886610565</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/processed_data/Video_466_EXP5_FAPS4_40V/contracciones.xlsx
+++ b/data/processed_data/Video_466_EXP5_FAPS4_40V/contracciones.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
         <v>0.6349</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -459,13 +459,13 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8466</v>
+        <v>0.6984</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -473,13 +473,13 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.7683</v>
+      </c>
+      <c r="C4" t="n">
         <v>6</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1.2698</v>
-      </c>
-      <c r="C4" t="n">
-        <v>5</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -487,10 +487,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>3.993</v>
       </c>
       <c r="B5" t="n">
-        <v>1.6931</v>
+        <v>0.8451</v>
       </c>
       <c r="C5" t="n">
         <v>5</v>
@@ -501,10 +501,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10</v>
+        <v>4.392</v>
       </c>
       <c r="B6" t="n">
-        <v>2.1164</v>
+        <v>0.9295</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
@@ -515,10 +515,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>12</v>
+        <v>4.832</v>
       </c>
       <c r="B7" t="n">
-        <v>2.5397</v>
+        <v>1.0227</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
@@ -529,10 +529,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>15</v>
+        <v>5.315</v>
       </c>
       <c r="B8" t="n">
-        <v>3.1746</v>
+        <v>1.1249</v>
       </c>
       <c r="C8" t="n">
         <v>5</v>
@@ -543,15 +543,225 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20</v>
+        <v>5.846</v>
       </c>
       <c r="B9" t="n">
-        <v>4.2328</v>
+        <v>1.2373</v>
       </c>
       <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6.431</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1.3611</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7.074</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1.4971</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7.781</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1.6468</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8.558999999999999</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1.8114</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9.414999999999999</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1.9926</v>
+      </c>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10.357</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2.192</v>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11.392</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2.411</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12.532</v>
+      </c>
+      <c r="B17" t="n">
+        <v>2.6523</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13.785</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2.9175</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>15.163</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3.2091</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3.5302</v>
+      </c>
+      <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>18.348</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3.8832</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20.182</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4.2713</v>
+      </c>
+      <c r="C22" t="n">
         <v>3</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22.201</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4.6986</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>24.421</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5.1685</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -566,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR2"/>
+  <dimension ref="A1:BB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -642,152 +852,202 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>picos_con_sep_menor</t>
+          <t>intervalo_mediano_s</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>intervalo_mediano_s</t>
+          <t>amplitud_traslacion_px</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>amplitud_traslacion_px</t>
+          <t>ritmo</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>ritmo</t>
+          <t>fps_medido</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>fps_medido</t>
+          <t>adelgazamiento_px</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>adelgazamiento_px</t>
+          <t>adelgazamiento_sigma</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>adelgazamiento_sigma</t>
+          <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>retardo_adelgazamiento_s</t>
+          <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>cociente_adelg_trasl_pct</t>
+          <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>adelgazamiento_robusto_px</t>
+          <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>adelgazamiento_robusto_sigma</t>
+          <t>cociente_robusto_pct</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>cociente_robusto_pct</t>
+          <t>cinetica_min_frames</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>cinetica_min_frames</t>
+          <t>amplitud_relativa_pct</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>amplitud_relativa_pct</t>
+          <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>amplitud_relativa_iqr_pct</t>
+          <t>ttp_n_eventos</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>ttp_n_eventos</t>
+          <t>ttp_frames_mediana</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>ttp_frames_mediana</t>
+          <t>ttp_reportable</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>ttp_reportable</t>
+          <t>ttp_s</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>ttp_s</t>
+          <t>ttp_iqr_s</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>ttp_iqr_s</t>
+          <t>ttp_cota_inf_s</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>ttp_cota_inf_s</t>
+          <t>ttp_cota_sup_s</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>ttp_cota_sup_s</t>
+          <t>rt50_n_eventos</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>rt50_n_eventos</t>
+          <t>rt50_frames_mediana</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>rt50_frames_mediana</t>
+          <t>rt50_reportable</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>rt50_reportable</t>
+          <t>rt50_s</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>rt50_s</t>
+          <t>rt50_iqr_s</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>rt50_iqr_s</t>
+          <t>rt50_cota_inf_s</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>rt50_cota_inf_s</t>
+          <t>rt50_cota_sup_s</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>rt50_cota_sup_s</t>
+          <t>cinetica_motivo</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>cinetica_motivo</t>
+          <t>fotogramas_sin_medida</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>fotogramas_sin_medida_pct</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>fotogramas_low_quality</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>eventos_junto_a_hueco</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>win_s_usado</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>win_s_automatico</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>duracion_evento_max_s</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>ventana_corta</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>conteo_por_ventana</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>conteo_estable_ventana</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>mesetas</t>
         </is>
       </c>
     </row>
@@ -819,7 +1079,7 @@
         <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>8.558999999999999</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -829,27 +1089,24 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>meseta de 5 eventos en k=4..15 (6 puntos) con 0 falsos de control</t>
+          <t>meseta de 5 eventos en k=3.993..16.68 (x4.18) con 0 falsos de control</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>4-15</t>
+          <t>3.993-16.68</t>
         </is>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>7</v>
+        <v>9.987500000000004</v>
       </c>
       <c r="P2" t="n">
-        <v>9.987500000000004</v>
-      </c>
-      <c r="Q2" t="n">
         <v>4.293600000000026</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>{'n_eventos': 5, 'hay_estimulacion': True, 'estimulados': array([0, 1, 2, 3, 4]), 'espontaneos': array([], dtype=int64), 'z': 13.577, 'p_valor': nan, 'periodo_grilla_s': 10.0287, 'periodo_s': 9.99433, 'periodo_err_s': 0.01197, 'frecuencia_Hz': 0.10006, 'frecuencia_err_Hz': 0.00012, 'jitter_s': 0.03509, 'tolerancia_s': 0.1071, 'n_estimulados': 5, 'n_ranuras': 5, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 14.312, 'tren_fin_s': 54.322, 'estimulados_dudosos': array([], dtype=int64), 'resumen_grupos':          grupo  n  ...  amplitud_mediana_px  amplitud_IQR_px
 0  estimulados  5  ...               4.2936           0.4583
@@ -863,90 +1120,127 @@
 4       5       54.2833     54.3217  0.03833       True}</t>
         </is>
       </c>
+      <c r="R2" t="n">
+        <v>30.00000000000171</v>
+      </c>
       <c r="S2" t="n">
-        <v>30.00000000000171</v>
+        <v>0.7528916758085472</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7528916758085472</v>
+        <v>4.612481597350608</v>
       </c>
       <c r="U2" t="n">
-        <v>4.612481597350608</v>
+        <v>-0.5999999999999659</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5999999999999659</v>
+        <v>17.9196777280517</v>
       </c>
       <c r="W2" t="n">
-        <v>17.9196777280517</v>
+        <v>0.2633470245440738</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2633470245440738</v>
+        <v>2.794416867623182</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.794416867623182</v>
+        <v>6.26795854184891</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.26795854184891</v>
+        <v>5</v>
       </c>
       <c r="AA2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB2" t="n">
         <v>2.134093296607975</v>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>1.97-2.195</t>
         </is>
       </c>
+      <c r="AC2" t="n">
+        <v>5</v>
+      </c>
       <c r="AD2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE2" t="n">
         <v>9</v>
       </c>
-      <c r="AF2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG2" t="n">
+      <c r="AE2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
         <v>0.2842709976597053</v>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.2563-0.2903</t>
         </is>
       </c>
+      <c r="AH2" t="n">
+        <v>0.1366666666666596</v>
+      </c>
       <c r="AI2" t="n">
-        <v>0.1366666666666596</v>
+        <v>0.3649999999999984</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.3649999999999984</v>
+        <v>5</v>
       </c>
       <c r="AK2" t="n">
         <v>5</v>
       </c>
-      <c r="AL2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN2" t="n">
+      <c r="AL2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="n">
         <v>0.1600804817649646</v>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>0.1445-0.1607</t>
         </is>
       </c>
+      <c r="AO2" t="n">
+        <v>0.07000000000000028</v>
+      </c>
       <c r="AP2" t="n">
-        <v>0.07000000000000028</v>
-      </c>
-      <c r="AQ2" t="n">
         <v>0.2600000000000016</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>TTP y RT50 medibles</t>
+        </is>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.5999999999999659</v>
+      </c>
+      <c r="AY2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>1.5 s: 5 | 2 s: 5 | 3 s: 5</t>
+        </is>
+      </c>
+      <c r="BA2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>5 ev en k=3.993-16.68</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1206,6 +1500,11 @@
           <t>amplitud_px</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>junto_a_hueco</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1216,6 +1515,9 @@
       </c>
       <c r="C2" t="n">
         <v>3.863699999999994</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1228,6 +1530,9 @@
       <c r="C3" t="n">
         <v>3.965399999999988</v>
       </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1239,6 +1544,9 @@
       <c r="C4" t="n">
         <v>4.293600000000026</v>
       </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1250,6 +1558,9 @@
       <c r="C5" t="n">
         <v>4.461000000000013</v>
       </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1260,6 +1571,9 @@
       </c>
       <c r="C6" t="n">
         <v>4.423699999999997</v>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed_data/Video_466_EXP5_FAPS4_40V/contracciones.xlsx
+++ b/data/processed_data/Video_466_EXP5_FAPS4_40V/contracciones.xlsx
@@ -1,18 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="estab_Video_466_EXP5_FAPS4" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumen_Video_466_EXP5_FAP" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ritmo_Video_466_EXP5_FAPS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="grilla_Video_466_EXP5_FAP" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eventos_Video_466_EXP5_FAP" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cinetica_Video_466_EXP5_FAP" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="estab_Video_466_EXP5_FAPS4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="resumen_Video_466_EXP5_FAP" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ritmo_Video_466_EXP5_FAPS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="trenes_Video_466_EXP5_FAP" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="grilla_Video_466_EXP5_FAP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="eventos_Video_466_EXP5_FAP" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="cinetica_Video_466_EXP5_FAP" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="cin_grupos_Video_466_EXP5_F" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,13 +24,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,12 +52,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,22 +436,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -448,13 +462,13 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6349</v>
+        <v>0.5473</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -462,13 +476,13 @@
         <v>3.3</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6984</v>
+        <v>0.602</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -476,13 +490,13 @@
         <v>3.63</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7683</v>
+        <v>0.6622</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -490,13 +504,13 @@
         <v>3.993</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8451</v>
+        <v>0.7285</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -504,13 +518,13 @@
         <v>4.392</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9295</v>
+        <v>0.8012</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -518,13 +532,13 @@
         <v>4.832</v>
       </c>
       <c r="B7" t="n">
-        <v>1.0227</v>
+        <v>0.8815</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -532,13 +546,13 @@
         <v>5.315</v>
       </c>
       <c r="B8" t="n">
-        <v>1.1249</v>
+        <v>0.9696</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -546,10 +560,10 @@
         <v>5.846</v>
       </c>
       <c r="B9" t="n">
-        <v>1.2373</v>
+        <v>1.0665</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -560,7 +574,7 @@
         <v>6.431</v>
       </c>
       <c r="B10" t="n">
-        <v>1.3611</v>
+        <v>1.1732</v>
       </c>
       <c r="C10" t="n">
         <v>5</v>
@@ -574,7 +588,7 @@
         <v>7.074</v>
       </c>
       <c r="B11" t="n">
-        <v>1.4971</v>
+        <v>1.2905</v>
       </c>
       <c r="C11" t="n">
         <v>5</v>
@@ -588,7 +602,7 @@
         <v>7.781</v>
       </c>
       <c r="B12" t="n">
-        <v>1.6468</v>
+        <v>1.4195</v>
       </c>
       <c r="C12" t="n">
         <v>5</v>
@@ -602,7 +616,7 @@
         <v>8.558999999999999</v>
       </c>
       <c r="B13" t="n">
-        <v>1.8114</v>
+        <v>1.5615</v>
       </c>
       <c r="C13" t="n">
         <v>5</v>
@@ -616,7 +630,7 @@
         <v>9.414999999999999</v>
       </c>
       <c r="B14" t="n">
-        <v>1.9926</v>
+        <v>1.7176</v>
       </c>
       <c r="C14" t="n">
         <v>5</v>
@@ -630,7 +644,7 @@
         <v>10.357</v>
       </c>
       <c r="B15" t="n">
-        <v>2.192</v>
+        <v>1.8895</v>
       </c>
       <c r="C15" t="n">
         <v>5</v>
@@ -644,7 +658,7 @@
         <v>11.392</v>
       </c>
       <c r="B16" t="n">
-        <v>2.411</v>
+        <v>2.0783</v>
       </c>
       <c r="C16" t="n">
         <v>5</v>
@@ -658,7 +672,7 @@
         <v>12.532</v>
       </c>
       <c r="B17" t="n">
-        <v>2.6523</v>
+        <v>2.2863</v>
       </c>
       <c r="C17" t="n">
         <v>5</v>
@@ -672,7 +686,7 @@
         <v>13.785</v>
       </c>
       <c r="B18" t="n">
-        <v>2.9175</v>
+        <v>2.5149</v>
       </c>
       <c r="C18" t="n">
         <v>5</v>
@@ -686,7 +700,7 @@
         <v>15.163</v>
       </c>
       <c r="B19" t="n">
-        <v>3.2091</v>
+        <v>2.7662</v>
       </c>
       <c r="C19" t="n">
         <v>5</v>
@@ -700,7 +714,7 @@
         <v>16.68</v>
       </c>
       <c r="B20" t="n">
-        <v>3.5302</v>
+        <v>3.043</v>
       </c>
       <c r="C20" t="n">
         <v>5</v>
@@ -714,10 +728,10 @@
         <v>18.348</v>
       </c>
       <c r="B21" t="n">
-        <v>3.8832</v>
+        <v>3.3473</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -728,10 +742,10 @@
         <v>20.182</v>
       </c>
       <c r="B22" t="n">
-        <v>4.2713</v>
+        <v>3.6819</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -742,10 +756,10 @@
         <v>22.201</v>
       </c>
       <c r="B23" t="n">
-        <v>4.6986</v>
+        <v>4.0502</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -756,10 +770,10 @@
         <v>24.421</v>
       </c>
       <c r="B24" t="n">
-        <v>5.1685</v>
+        <v>4.4552</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -776,278 +790,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB2"/>
+  <dimension ref="A1:BI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>k_usado</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>k_automatico</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>hay_meseta</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>meseta_motivo</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>meseta_k_rango</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>conteo_reportable</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>amplitud_traslacion_px</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ritmo</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>fps_medido</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>adelgazamiento_px</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>adelgazamiento_sigma</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>cinetica_grupo_principal</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>n_eventos_cinetica</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_n_medibles</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_n_medibles</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>mesetas</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>ruido_borde_sup_px</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>ruido_borde_inf_px</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>cociente_ruido_bordes</t>
         </is>
       </c>
     </row>
@@ -1070,16 +1119,16 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2116411499999676</v>
+        <v>0.1824339300000093</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3649915845233185</v>
+        <v>0.2826740078304275</v>
       </c>
       <c r="H2" t="n">
         <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>8.558999999999999</v>
+        <v>11.392</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -1089,159 +1138,189 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>meseta de 5 eventos en k=3.993..16.68 (x4.18) con 0 falsos de control</t>
+          <t>meseta de 5 eventos en k=6.431..20.182 (x3.14) con 0 falsos de control</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>3.993-16.68</t>
+          <t>6.431-20.182</t>
         </is>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>9.987500000000004</v>
+        <v>10.01166666666666</v>
       </c>
       <c r="P2" t="n">
-        <v>4.293600000000026</v>
+        <v>4.358199999999954</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'n_eventos': 5, 'hay_estimulacion': True, 'estimulados': array([0, 1, 2, 3, 4]), 'espontaneos': array([], dtype=int64), 'z': 13.577, 'p_valor': nan, 'periodo_grilla_s': 10.0287, 'periodo_s': 9.99433, 'periodo_err_s': 0.01197, 'frecuencia_Hz': 0.10006, 'frecuencia_err_Hz': 0.00012, 'jitter_s': 0.03509, 'tolerancia_s': 0.1071, 'n_estimulados': 5, 'n_ranuras': 5, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 14.312, 'tren_fin_s': 54.322, 'estimulados_dudosos': array([], dtype=int64), 'resumen_grupos':          grupo  n  ...  amplitud_mediana_px  amplitud_IQR_px
-0  estimulados  5  ...               4.2936           0.4583
+          <t>{'n_eventos': 5, 'fuente_tiempo': 'inicio (onset 10 %) en 5 de 5 eventos; pico en el resto', 'modo_busqueda': 'dirigida', 'trenes':    tren           busqueda  ... inicio_s   fin_s
+0     1  dirigida a 0.1 Hz  ...   14.028  54.022
+[1 rows x 17 columns], 'dudosos': Empty DataFrame
+Columns: []
+Index: [], 'sacados_tiempo_amplitud': Empty DataFrame
+Columns: []
+Index: [], 'grupo_por_evento': array(['estimulados', 'estimulados', 'estimulados', 'estimulados',
+       'estimulados'], dtype=object), 'tren_por_evento': array([1, 1, 1, 1, 1]), 'estimulados': array([0, 1, 2, 3, 4]), 'estimulados_dudosos': array([], dtype=int64), 'espontaneos': array([], dtype=int64), 'hay_estimulacion': True, 'n_trenes_estimulados': 1, 'tren_principal': 1, 'veredicto': 'enganchado a la frecuencia configurada (0.1 Hz)', 'z': 17.247, 'p_valor': 0.000999000999000999, 'periodo_grilla_s': 9.9716, 'periodo_s': 10.00184, 'periodo_err_s': 0.00542, 'frecuencia_Hz': 0.09998, 'frecuencia_err_Hz': 5.4e-05, 'jitter_s': 0.01189, 'tolerancia_s': 0.0667, 'n_estimulados': 5, 'n_ranuras': 5, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 14.028, 'tren_fin_s': 54.022, 'resumen_grupos':          grupo  n  t_inicio_s  ...  CV_intervalo_pct  amplitud_mediana_px  amplitud_IQR_px
+0  estimulados  5       14.03  ...               0.3               4.3582            0.346
 [1 rows x 10 columns], 'espontaneas_instantanea': Empty DataFrame
 Columns: [tiempo_s, intervalo_s, frecuencia_Hz]
-Index: [], 'grilla':    ranura  t_esperado_s  t_medido_s  error_s  capturada
-0       1       14.3060     14.3117  0.00567       True
-1       2       24.3003     24.3200  0.01967       True
-2       3       34.2947     34.2767 -0.01800       True
-3       4       44.2890     44.2433 -0.04567       True
-4       5       54.2833     54.3217  0.03833       True}</t>
+Index: [], 'grilla':    tren  ranura  t_esperado_s  t_medido_s  error_s  capturada
+0     1       1       14.0280     14.0283  0.00033       True
+1     1       2       24.0298     24.0279 -0.00199       True
+2     1       3       34.0317     34.0217 -0.01000       True
+3     1       4       44.0335     44.0582  0.02466       True
+4     1       5       54.0354     54.0224 -0.01300       True}</t>
         </is>
       </c>
       <c r="R2" t="n">
         <v>30.00000000000171</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7528916758085472</v>
+        <v>0.5942693318869147</v>
       </c>
       <c r="T2" t="n">
-        <v>4.612481597350608</v>
+        <v>4.700915493580403</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5999999999999659</v>
+        <v>-0.06666666666666288</v>
       </c>
       <c r="V2" t="n">
-        <v>17.9196777280517</v>
+        <v>13.61841116952774</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2633470245440738</v>
+        <v>0.2389841514271609</v>
       </c>
       <c r="X2" t="n">
-        <v>2.794416867623182</v>
+        <v>3.274378304496076</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.26795854184891</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>5</v>
+        <v>5.476615168415056</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
       </c>
       <c r="AA2" t="n">
-        <v>2.134093296607975</v>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>1.97-2.195</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>5</v>
       </c>
       <c r="AC2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE2" t="b">
-        <v>1</v>
+        <v>2.164354196058185</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2.127-2.3</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>5</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2842709976597053</v>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0.2563-0.2903</t>
-        </is>
-      </c>
-      <c r="AH2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.2549890109890072</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.2543-0.2852</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
         <v>0.1366666666666596</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AL2" t="n">
         <v>0.3649999999999984</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL2" t="b">
-        <v>1</v>
-      </c>
       <c r="AM2" t="n">
-        <v>0.1600804817649646</v>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.1445-0.1607</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>3</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.07000000000000028</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0.2600000000000016</v>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>TTP y RT50 medibles</t>
-        </is>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.1920369393139794</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.175-0.1952</t>
+        </is>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>0.03333333333333854</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
+        <v>0.259999999999998</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>RT50: mediana sobre los 3 de 5 eventos medibles</t>
+        </is>
       </c>
       <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>2</v>
       </c>
-      <c r="AW2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.5999999999999659</v>
-      </c>
-      <c r="AY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="BA2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0.5666666666666345</v>
+      </c>
+      <c r="BC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="inlineStr">
         <is>
           <t>1.5 s: 5 | 2 s: 5 | 3 s: 5</t>
         </is>
       </c>
-      <c r="BA2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>5 ev en k=3.993-16.68</t>
-        </is>
+      <c r="BE2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>5 ev en k=6.431-20.182</t>
+        </is>
+      </c>
+      <c r="BG2" t="n">
+        <v>0.3023021400000065</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0.1772448300000057</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.705562526139673</v>
       </c>
     </row>
   </sheetData>
@@ -1259,52 +1338,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>t_inicio_s</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>t_fin_s</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>intervalo_IQR_s</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>frecuencia_mediana_Hz</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>CV_intervalo_pct</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>amplitud_mediana_px</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>amplitud_IQR_px</t>
         </is>
@@ -1320,28 +1399,28 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>14.31</v>
+        <v>14.03</v>
       </c>
       <c r="D2" t="n">
-        <v>54.32</v>
+        <v>54.02</v>
       </c>
       <c r="E2" t="n">
-        <v>9.987500000000001</v>
+        <v>9.996700000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0617</v>
+        <v>0.0224</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1001</v>
+        <v>0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I2" t="n">
-        <v>4.2936</v>
+        <v>4.3582</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4583</v>
+        <v>0.346</v>
       </c>
     </row>
   </sheetData>
@@ -1355,33 +1434,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ranura</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>t_esperado_s</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>t_medido_s</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>error_s</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>capturada</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tren</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>busqueda</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>veredicto</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>clasificacion</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>periodo_s</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>periodo_err_s</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>frecuencia_Hz</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>jitter_ms</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>z</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>p_valor</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>n_eventos_tren</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>n_ranuras</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>captura_pct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>n_dudosos</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>n_sacados_tiempo_amplitud</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>inicio_s</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>fin_s</t>
         </is>
       </c>
     </row>
@@ -1389,85 +1528,59 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
-        <v>14.306</v>
-      </c>
-      <c r="C2" t="n">
-        <v>14.3117</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.00567</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>24.3003</v>
-      </c>
-      <c r="C3" t="n">
-        <v>24.32</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.01967</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>34.2947</v>
-      </c>
-      <c r="C4" t="n">
-        <v>34.2767</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-0.018</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>44.289</v>
-      </c>
-      <c r="C5" t="n">
-        <v>44.2433</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-0.04567</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>54.2833</v>
-      </c>
-      <c r="C6" t="n">
-        <v>54.3217</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.03833</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>dirigida a 0.1 Hz</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>enganchado a la frecuencia configurada (0.1 Hz)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>10.00184</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.00542</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.09998</v>
+      </c>
+      <c r="H2" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="I2" t="n">
+        <v>17.247</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>100</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>14.028</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>54.022</v>
       </c>
     </row>
   </sheetData>
@@ -1481,28 +1594,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>evento</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>tiempo_s</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>amplitud_px</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>junto_a_hueco</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tren</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ranura</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>t_esperado_s</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>t_medido_s</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>error_s</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>capturada</t>
         </is>
       </c>
     </row>
@@ -1511,69 +1634,99 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>14.31166666666667</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.863699999999994</v>
-      </c>
-      <c r="D2" t="b">
-        <v>0</v>
+        <v>14.028</v>
+      </c>
+      <c r="D2" t="n">
+        <v>14.0283</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.00033</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>24.32</v>
-      </c>
       <c r="C3" t="n">
-        <v>3.965399999999988</v>
-      </c>
-      <c r="D3" t="b">
-        <v>0</v>
+        <v>24.0298</v>
+      </c>
+      <c r="D3" t="n">
+        <v>24.0279</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.00199</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>34.27666666666667</v>
-      </c>
       <c r="C4" t="n">
-        <v>4.293600000000026</v>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
+        <v>34.0317</v>
+      </c>
+      <c r="D4" t="n">
+        <v>34.0217</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>44.24333333333335</v>
-      </c>
       <c r="C5" t="n">
-        <v>4.461000000000013</v>
-      </c>
-      <c r="D5" t="b">
-        <v>0</v>
+        <v>44.0335</v>
+      </c>
+      <c r="D5" t="n">
+        <v>44.0582</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.02466</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>54.32166666666667</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>4.423699999999997</v>
-      </c>
-      <c r="D6" t="b">
-        <v>0</v>
+        <v>54.0354</v>
+      </c>
+      <c r="D6" t="n">
+        <v>54.0224</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1587,118 +1740,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>grupo</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>frame_pico</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>grosor_reposo_px</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>amplitud_relativa_pct</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>meseta_pico_frames</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>onset_s</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>ttp_frames</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ttp_s</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ttp_min_s</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ttp_max_s</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ttp_medible</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>rt50_frames</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>rt50_s</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>rt50_min_s</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>rt50_max_s</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>rt50_medible</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>offset_s</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>duracion_frames</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>duracion_s</t>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>junto_a_hueco</t>
         </is>
       </c>
     </row>
@@ -1706,350 +1769,848 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>estimulados</t>
-        </is>
+      <c r="B2" t="n">
+        <v>14.24333333333333</v>
       </c>
       <c r="C2" t="n">
-        <v>422</v>
-      </c>
-      <c r="D2" t="n">
-        <v>14.31166666666667</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3.863699999999994</v>
-      </c>
-      <c r="F2" t="n">
-        <v>201.1121664868647</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.921166713826011</v>
-      </c>
-      <c r="H2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>14.02739566900696</v>
-      </c>
-      <c r="J2" t="n">
-        <v>9</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.2842709976597053</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.1366666666666596</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.3766666666666705</v>
-      </c>
-      <c r="N2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.1249238736546019</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.02500000000000036</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.2700000000000014</v>
-      </c>
-      <c r="S2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>14.64498546625815</v>
-      </c>
-      <c r="U2" t="n">
-        <v>20</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.6175897972511848</v>
+        <v>3.873699999999985</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>estimulados</t>
-        </is>
+      <c r="B3" t="n">
+        <v>24.32</v>
       </c>
       <c r="C3" t="n">
-        <v>706</v>
-      </c>
-      <c r="D3" t="n">
-        <v>24.32</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3.965399999999988</v>
-      </c>
-      <c r="F3" t="n">
-        <v>201.2503244797527</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.970381916278072</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I3" t="n">
-        <v>24.02968855374078</v>
-      </c>
-      <c r="J3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.2903114462592171</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.1733333333333285</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.3649999999999984</v>
-      </c>
-      <c r="N3" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>5</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.1444839255499204</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.07000000000000028</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.2600000000000016</v>
-      </c>
-      <c r="S3" t="b">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>24.60785822401614</v>
-      </c>
-      <c r="U3" t="n">
-        <v>18</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.5781696702753614</v>
+        <v>4.669500000000028</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>estimulados</t>
-        </is>
+      <c r="B4" t="n">
+        <v>34.27666666666667</v>
       </c>
       <c r="C4" t="n">
-        <v>999</v>
-      </c>
-      <c r="D4" t="n">
-        <v>34.27666666666667</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4.293600000000026</v>
-      </c>
-      <c r="F4" t="n">
-        <v>201.1908292305903</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.134093296607975</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>34.02041304655842</v>
-      </c>
-      <c r="J4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.2562536201082466</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.2050000000000054</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.36666666666666</v>
-      </c>
-      <c r="N4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.1607267264372325</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.03333333333333854</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.2066666666666706</v>
-      </c>
-      <c r="S4" t="b">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>34.59467108043386</v>
-      </c>
-      <c r="U4" t="n">
-        <v>18</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.5742580338754379</v>
+        <v>4.358199999999954</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>estimulados</t>
-        </is>
+      <c r="B5" t="n">
+        <v>44.34333333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>1275</v>
-      </c>
-      <c r="D5" t="n">
-        <v>44.24333333333335</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4.461000000000013</v>
-      </c>
-      <c r="F5" t="n">
-        <v>201.4650776355367</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.214279542814983</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>44.06655207232594</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.176781261007406</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.1033333333333317</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.2433333333333323</v>
-      </c>
-      <c r="N5" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>6</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.1913054372893299</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.123333333333342</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.259999999999998</v>
-      </c>
-      <c r="S5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>44.6152236135957</v>
-      </c>
-      <c r="U5" t="n">
-        <v>18</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.548671541269762</v>
+        <v>4.285599999999988</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
+      <c r="B6" t="n">
+        <v>54.27666666666667</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4.631599999999992</v>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>evento</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>grupo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tren</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>frame_pico</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tiempo_s</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>grosor_reposo_px</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>meseta_pico_frames</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>onset_s</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_frames</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_min_s</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_s</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_medible</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_frames</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_min_s</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_max_s</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_medible</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>offset_s</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>duracion_frames</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>duracion_s</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>420</v>
+      </c>
+      <c r="E2" t="n">
+        <v>14.24333333333333</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3.873699999999985</v>
+      </c>
+      <c r="G2" t="n">
+        <v>201.2478806612661</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.924840146028703</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14.02832670324646</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.215006630086874</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1366666666666596</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.3766666666666705</v>
+      </c>
+      <c r="O2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.1983675000987493</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.02500000000000036</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.2700000000000014</v>
+      </c>
+      <c r="T2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>14.6315440736754</v>
+      </c>
+      <c r="V2" t="n">
+        <v>19</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.6032173704289399</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>706</v>
+      </c>
+      <c r="E3" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4.669500000000028</v>
+      </c>
+      <c r="G3" t="n">
+        <v>201.1517691000594</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.321381522464894</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>24.02785434243768</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.2921456575623189</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1733333333333285</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.3649999999999984</v>
+      </c>
+      <c r="O3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1195689730485334</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.04500000000000171</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2300000000000004</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>24.64548552960188</v>
+      </c>
+      <c r="V3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.6176311871641964</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>34.27666666666667</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4.358199999999954</v>
+      </c>
+      <c r="G4" t="n">
+        <v>201.3626054338655</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.164354196058185</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.02167765567766</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.2549890109890072</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2050000000000054</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.36666666666666</v>
+      </c>
+      <c r="O4" t="b">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1580046645138182</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.03333333333333854</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.2066666666666706</v>
+      </c>
+      <c r="T4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>34.58778023249697</v>
+      </c>
+      <c r="V4" t="n">
+        <v>18</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.5661025768193113</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1278</v>
+      </c>
+      <c r="E5" t="n">
+        <v>44.34333333333333</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.285599999999988</v>
+      </c>
+      <c r="G5" t="n">
+        <v>201.470016369198</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.127165161959652</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>44.05817923850575</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.2851540948275755</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1033333333333317</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.3433333333333337</v>
+      </c>
+      <c r="O5" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.08952753779698241</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.02333333333334053</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.259999999999998</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>44.61379346241932</v>
+      </c>
+      <c r="V5" t="n">
+        <v>18</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.5556142239135653</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>estimulados</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1562</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>54.32166666666667</v>
+        <v>1561</v>
       </c>
       <c r="E6" t="n">
-        <v>4.423699999999997</v>
+        <v>54.27666666666667</v>
       </c>
       <c r="F6" t="n">
-        <v>201.5348332891158</v>
+        <v>4.631599999999992</v>
       </c>
       <c r="G6" t="n">
-        <v>2.195005165014769</v>
+        <v>201.3795777713071</v>
       </c>
       <c r="H6" t="n">
+        <v>2.299935301910197</v>
+      </c>
+      <c r="I6" t="n">
         <v>6</v>
       </c>
-      <c r="I6" t="n">
-        <v>54.02018076923077</v>
-      </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>54.02236536266862</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3014858974359029</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
+        <v>0.2543013039980551</v>
+      </c>
+      <c r="M6" t="n">
         <v>0.1000000000000014</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>0.3616666666666717</v>
       </c>
-      <c r="N6" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
+      <c r="O6" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
         <v>6</v>
       </c>
-      <c r="P6" t="n">
-        <v>0.1600804817649646</v>
-      </c>
       <c r="Q6" t="n">
-        <v>0.09999999999999432</v>
+        <v>0.1920369393139794</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3783333333333303</v>
-      </c>
-      <c r="S6" t="b">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>54.69892963533642</v>
+        <v>0.07000000000000028</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.3333333333333286</v>
+      </c>
+      <c r="T6" t="b">
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>21</v>
+        <v>54.67446774193549</v>
       </c>
       <c r="V6" t="n">
-        <v>0.67874886610565</v>
+        <v>20</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.6521023792668714</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>grupo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cinetica_min_frames</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>n_eventos_cinetica</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_iqr_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_n_eventos</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_n_medibles</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_frames_mediana</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_reportable</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_iqr_s</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_n_eventos</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_n_medibles</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_frames_mediana</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_reportable</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_iqr_s</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>cinetica_motivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>todos</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.164354196058185</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2.127-2.3</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2549890109890072</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.2543-0.2852</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.1366666666666596</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.3649999999999984</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.1920369393139794</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.175-0.1952</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>0.03333333333333854</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.259999999999998</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>RT50: mediana sobre los 3 de 5 eventos medibles</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.164354196058185</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2.127-2.3</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2549890109890072</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.2543-0.2852</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1366666666666596</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.3649999999999984</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.1920369393139794</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.175-0.1952</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>0.03333333333333854</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.259999999999998</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>RT50: mediana sobre los 3 de 5 eventos medibles</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/processed_data/Video_466_EXP5_FAPS4_40V/contracciones.xlsx
+++ b/data/processed_data/Video_466_EXP5_FAPS4_40V/contracciones.xlsx
@@ -24,16 +24,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -44,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -52,21 +49,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,22 +424,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -790,311 +778,316 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI2"/>
+  <dimension ref="A1:BJ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>k_usado</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>k_automatico</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>hay_meseta</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>meseta_motivo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>meseta_k_rango</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>conteo_reportable</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>amplitud_traslacion_px</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ritmo</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>fps_medido</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>adelgazamiento_px</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>adelgazamiento_sigma</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>cinetica_grupo_principal</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>eventos_junto_al_borde</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>mesetas</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>ruido_borde_sup_px</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>ruido_borde_inf_px</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>cociente_ruido_bordes</t>
         </is>
@@ -1289,37 +1282,40 @@
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
         <v>2</v>
       </c>
-      <c r="BA2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB2" t="n">
+      <c r="BB2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC2" t="n">
         <v>0.5666666666666345</v>
       </c>
-      <c r="BC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="inlineStr">
         <is>
           <t>1.5 s: 5 | 2 s: 5 | 3 s: 5</t>
         </is>
       </c>
-      <c r="BE2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BF2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BG2" t="inlineStr">
         <is>
           <t>5 ev en k=6.431-20.182</t>
         </is>
       </c>
-      <c r="BG2" t="n">
+      <c r="BH2" t="n">
         <v>0.3023021400000065</v>
       </c>
-      <c r="BH2" t="n">
+      <c r="BI2" t="n">
         <v>0.1772448300000057</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BJ2" t="n">
         <v>1.705562526139673</v>
       </c>
     </row>
@@ -1338,52 +1334,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_inicio_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_fin_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>intervalo_IQR_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_mediana_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>CV_intervalo_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>amplitud_mediana_px</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>amplitud_IQR_px</t>
         </is>
@@ -1438,87 +1434,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>busqueda</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>veredicto</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>clasificacion</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>periodo_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>periodo_err_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>jitter_ms</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>p_valor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>n_eventos_tren</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>n_ranuras</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>captura_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>n_dudosos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>n_sacados_tiempo_amplitud</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inicio_s</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>fin_s</t>
         </is>
@@ -1598,32 +1594,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ranura</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_esperado_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_medido_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>error_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>capturada</t>
         </is>
@@ -1740,28 +1736,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>junto_a_hueco</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>junto_al_borde</t>
         </is>
       </c>
     </row>
@@ -1776,6 +1777,9 @@
         <v>3.873699999999985</v>
       </c>
       <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1792,6 +1796,9 @@
       <c r="D3" t="b">
         <v>0</v>
       </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1806,6 +1813,9 @@
       <c r="D4" t="b">
         <v>0</v>
       </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1820,6 +1830,9 @@
       <c r="D5" t="b">
         <v>0</v>
       </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1832,6 +1845,9 @@
         <v>4.631599999999992</v>
       </c>
       <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1850,117 +1866,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>frame_pico</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>grosor_reposo_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>meseta_pico_frames</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>onset_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_frames</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_min_s</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ttp_max_s</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ttp_medible</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_frames</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_min_s</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_max_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_medible</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>offset_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>duracion_frames</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
@@ -2346,112 +2362,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
